--- a/fhir/CodeSystem-ehealth-program.xlsx
+++ b/fhir/CodeSystem-ehealth-program.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -163,6 +163,42 @@
   </si>
   <si>
     <t>Supportteam for Telemedicinsk monitoreringsapplikation</t>
+  </si>
+  <si>
+    <t>telma-konfiguration-1</t>
+  </si>
+  <si>
+    <t>Telma Konfiguration 1</t>
+  </si>
+  <si>
+    <t>Konfiguration 1 for Telemedicinsk monitoreringsapplikation</t>
+  </si>
+  <si>
+    <t>telma-konfiguration-2</t>
+  </si>
+  <si>
+    <t>Telma Konfiguration 2</t>
+  </si>
+  <si>
+    <t>Konfiguration 2 for Telemedicinsk monitoreringsapplikation</t>
+  </si>
+  <si>
+    <t>telma-konfiguration-3</t>
+  </si>
+  <si>
+    <t>Telma Konfiguration 3</t>
+  </si>
+  <si>
+    <t>Konfiguration 3 for Telemedicinsk monitoreringsapplikation</t>
+  </si>
+  <si>
+    <t>telma-konfiguration-4</t>
+  </si>
+  <si>
+    <t>Telma Konfiguration 4</t>
+  </si>
+  <si>
+    <t>Konfiguration 4 for Telemedicinsk monitoreringsapplikation</t>
   </si>
   <si>
     <t>fob</t>
@@ -479,7 +515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -552,6 +588,62 @@
         <v>52</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/fhir/CodeSystem-ehealth-program.xlsx
+++ b/fhir/CodeSystem-ehealth-program.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-program.xlsx
+++ b/fhir/CodeSystem-ehealth-program.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-program.xlsx
+++ b/fhir/CodeSystem-ehealth-program.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -208,6 +208,15 @@
   </si>
   <si>
     <t>Fællesoffentlig Behandlingsplatform</t>
+  </si>
+  <si>
+    <t>telesaar</t>
+  </si>
+  <si>
+    <t>Telesår</t>
+  </si>
+  <si>
+    <t>Telemedicinsk Sårvurdering</t>
   </si>
 </sst>
 </file>
@@ -515,7 +524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -644,6 +653,20 @@
         <v>64</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/fhir/CodeSystem-ehealth-program.xlsx
+++ b/fhir/CodeSystem-ehealth-program.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-program.xlsx
+++ b/fhir/CodeSystem-ehealth-program.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-program.xlsx
+++ b/fhir/CodeSystem-ehealth-program.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
